--- a/Ordersheet_input.xlsx
+++ b/Ordersheet_input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marc Zimmerli\Desktop\Stockpilebot_git_new\Stockpile_manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95519A5C-119A-4B38-934E-C1B425860047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D727D3-F8BD-47BC-A306-51ADF36C12CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{0D40ED5F-238A-4EF7-8D5C-B1E710F7D38A}"/>
   </bookViews>
@@ -7341,6 +7341,7 @@
     <sortCondition ref="A2:A454"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
